--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -549,7 +549,7 @@
         <v>92008.50999999999</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7750.32</v>
+        <v>7753.03</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
         <v>-7991.49</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>99758.83</v>
+        <v>99761.53999999999</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -574,16 +574,16 @@
         <v>0</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.002412</v>
+        <v>-0.002385</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.001088</v>
+        <v>0.001115</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.002412</v>
+        <v>-0.002385</v>
       </c>
     </row>
   </sheetData>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>7750.32</v>
+        <v>7753.03</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-241.17</v>
+        <v>-238.46</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.0302</v>
+        <v>-0.0298</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0.07770000000000001</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="5" t="n">
-        <v>35.240002</v>
+        <v>35.18</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.195906</v>
+        <v>0.195979</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.23469</v>
+        <v>1.235132</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.163873</v>
+        <v>1.16428</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1.355271</v>
+        <v>1.356043</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>35.240002</v>
+        <v>35.18</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -549,7 +549,7 @@
         <v>92008.50999999999</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7753.03</v>
+        <v>7751.23</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
         <v>-7991.49</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>99761.53999999999</v>
+        <v>99759.74000000001</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -574,16 +574,16 @@
         <v>0</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.002385</v>
+        <v>-0.002403</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.001115</v>
+        <v>0.001097</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.002385</v>
+        <v>-0.002403</v>
       </c>
     </row>
   </sheetData>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>7753.03</v>
+        <v>7751.23</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-238.46</v>
+        <v>-240.26</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.0298</v>
+        <v>-0.0301</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0.07770000000000001</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="5" t="n">
-        <v>35.18</v>
+        <v>35.150002</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.235132</v>
+        <v>1.234919</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.16428</v>
+        <v>1.164009</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1.356043</v>
+        <v>1.355693</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>35.18</v>
+        <v>35.150002</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -549,7 +549,7 @@
         <v>92008.50999999999</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7751.23</v>
+        <v>7752.13</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
         <v>-7991.49</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>99759.74000000001</v>
+        <v>99760.64</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -574,16 +574,16 @@
         <v>0</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.002403</v>
+        <v>-0.002394</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.001097</v>
+        <v>0.001106</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.002403</v>
+        <v>-0.002394</v>
       </c>
     </row>
   </sheetData>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>7751.23</v>
+        <v>7752.13</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-240.26</v>
+        <v>-239.36</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.0301</v>
+        <v>-0.03</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0.07770000000000001</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="5" t="n">
-        <v>35.150002</v>
+        <v>35.119999</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.195979</v>
+        <v>0.195998</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.234919</v>
+        <v>1.235132</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.164009</v>
+        <v>1.164144</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1.355693</v>
+        <v>1.35584</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>35.150002</v>
+        <v>35.119999</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -549,7 +549,7 @@
         <v>92008.50999999999</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7752.13</v>
+        <v>7750.32</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
         <v>-7991.49</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>99760.64</v>
+        <v>99758.83</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -574,16 +574,16 @@
         <v>0</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.002394</v>
+        <v>-0.002412</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.001106</v>
+        <v>0.001088</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.002394</v>
+        <v>-0.002412</v>
       </c>
     </row>
   </sheetData>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>7752.13</v>
+        <v>7750.32</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-239.36</v>
+        <v>-241.17</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.0302</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0.07770000000000001</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="5" t="n">
-        <v>35.119999</v>
+        <v>35.130001</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.195998</v>
+        <v>0.195971</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.235132</v>
+        <v>1.234827</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.164144</v>
+        <v>1.163873</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1.35584</v>
+        <v>1.355601</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>35.119999</v>
+        <v>35.130001</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -549,7 +549,7 @@
         <v>92007.99000000001</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7960.17</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
         <v>-7992.01</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>99968.16</v>
+        <v>92007.99000000001</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -569,21 +569,25 @@
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.000318</v>
+        <v>-0.07992</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.003182</v>
+        <v>-0.07642</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.000318</v>
+        <v>-0.07992</v>
       </c>
     </row>
   </sheetData>
@@ -755,32 +759,16 @@
       <c r="H2" s="3" t="n">
         <v>7992.01</v>
       </c>
-      <c r="I2" s="5" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>7960.17</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>-31.84</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>0.0796</v>
-      </c>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="P2" s="4" t="n">
-        <v>0.2729</v>
-      </c>
+      <c r="P2" s="4" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -831,7 +819,7 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>35.240002</v>
+        <v>35.080002</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -888,7 +876,7 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -1687,7 +1675,7 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.195906</v>
+        <v>0.195921</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1712,7 +1700,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.23469</v>
+        <v>1.236033</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1761,17 +1749,15 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>12.02</v>
-      </c>
+      <c r="C5" s="5" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>yfinance-no-close-on-2026-09-09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>missing</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1773,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1.355271</v>
+        <v>1.355142</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -1837,7 +1823,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -1862,7 +1848,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>35.240002</v>
+        <v>35.080002</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -588,6 +588,57 @@
       </c>
       <c r="O2" s="4" t="n">
         <v>-0.07992</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>92018.07000000001</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>92018.07000000001</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>-0.008463</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.000107</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>-0.079819</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>-0.071356</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>-0.079926</v>
       </c>
     </row>
   </sheetData>
@@ -775,7 +826,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -819,11 +870,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>35.080002</v>
+        <v>35.810001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -876,11 +927,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1626,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1861,6 +1912,204 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.195856</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.230254</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.161305</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.351151</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>145.830002</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>35.810001</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,57 @@
       </c>
       <c r="O3" s="4" t="n">
         <v>-0.079926</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>92028.16</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>92028.16</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>-0.00078</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.000215</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>-0.079718</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>-0.07893799999999999</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>-0.079933</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +877,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -870,11 +921,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>35.810001</v>
+        <v>34.560001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -927,11 +978,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1677,7 +1728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2110,6 +2161,204 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.195111</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.22534</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1.160227</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-11</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.352887</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>146.960007</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>34.560001</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
